--- a/NEW BOT 02/Semi_Finished_Inventory_Movement.xlsx
+++ b/NEW BOT 02/Semi_Finished_Inventory_Movement.xlsx
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Production Module ⟶ Advance Production Reports ⟶ Inventory Movement Report(221023) ⟶ Item Group: Semi Finished Goods  |  Company: FAN  |  Date Range: 2026-09-01 to 2026-09-19</t>
+          <t>Production Module ⟶ Advance Production Reports ⟶ Inventory Movement Report(221023) ⟶ Item Group: Semi Finished Goods  |  Company: FAN  |  Date Range: 2026-09-01 to 2026-09-21</t>
         </is>
       </c>
     </row>
@@ -639,13 +639,13 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>1,428,162.82</t>
+          <t>1,626,125.82</t>
         </is>
       </c>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>439,294.52</t>
+          <t>478,527.52</t>
         </is>
       </c>
       <c r="I5" s="4" t="n"/>
@@ -1186,25 +1186,25 @@
         <v>0</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>2070</v>
+        <v>3730</v>
       </c>
       <c r="L8" s="16" t="n">
-        <v>2293</v>
+        <v>3953</v>
       </c>
       <c r="M8" s="16" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="N8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O8" s="16" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>100</v>
+        <v>1622</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>100</v>
+        <v>1622</v>
       </c>
       <c r="R8" s="16" t="n">
         <v>0</v>
@@ -1257,25 +1257,25 @@
         <v>0</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>2125</v>
+        <v>2174</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>2282</v>
+        <v>2331</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="N9" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>2193</v>
+        <v>2331</v>
       </c>
       <c r="P9" s="19" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="19" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="R9" s="19" t="n">
         <v>0</v>
@@ -1328,25 +1328,25 @@
         <v>0</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>4150</v>
+        <v>5520</v>
       </c>
       <c r="L10" s="16" t="n">
-        <v>9030</v>
+        <v>10400</v>
       </c>
       <c r="M10" s="16" t="n">
-        <v>8756</v>
+        <v>9556</v>
       </c>
       <c r="N10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O10" s="16" t="n">
-        <v>8756</v>
+        <v>9556</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>274</v>
+        <v>844</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>274</v>
+        <v>844</v>
       </c>
       <c r="R10" s="16" t="n">
         <v>0</v>
@@ -1476,19 +1476,19 @@
         <v>11715</v>
       </c>
       <c r="M12" s="16" t="n">
-        <v>8580</v>
+        <v>9380</v>
       </c>
       <c r="N12" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="16" t="n">
-        <v>8580</v>
+        <v>9380</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>3135</v>
+        <v>2335</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>3135</v>
+        <v>2335</v>
       </c>
       <c r="R12" s="16" t="n">
         <v>0</v>
@@ -1683,25 +1683,25 @@
         <v>0</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>4414</v>
+        <v>4923</v>
       </c>
       <c r="L15" s="19" t="n">
-        <v>5504</v>
+        <v>6013</v>
       </c>
       <c r="M15" s="19" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="N15" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O15" s="19" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="P15" s="19" t="n">
-        <v>4</v>
+        <v>460</v>
       </c>
       <c r="Q15" s="19" t="n">
-        <v>4</v>
+        <v>460</v>
       </c>
       <c r="R15" s="19" t="n">
         <v>0</v>
@@ -1760,19 +1760,19 @@
         <v>5561</v>
       </c>
       <c r="M16" s="16" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="N16" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O16" s="16" t="n">
-        <v>5500</v>
+        <v>5553</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="Q16" s="16" t="n">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="R16" s="16" t="n">
         <v>0</v>
@@ -2109,28 +2109,28 @@
         <v>0</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>24300</v>
+        <v>42300</v>
       </c>
       <c r="L21" s="19" t="n">
-        <v>24958.821</v>
+        <v>42958.821</v>
       </c>
       <c r="M21" s="19" t="n">
-        <v>24558.5</v>
+        <v>42623.5</v>
       </c>
       <c r="N21" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="19" t="n">
-        <v>24558.5</v>
+        <v>42623.5</v>
       </c>
       <c r="P21" s="19" t="n">
-        <v>400.321</v>
+        <v>335.321</v>
       </c>
       <c r="Q21" s="19" t="n">
-        <v>400.321</v>
+        <v>335.321</v>
       </c>
       <c r="R21" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S21" s="18" t="inlineStr"/>
     </row>
@@ -2319,28 +2319,28 @@
         <v>0</v>
       </c>
       <c r="J24" s="16" t="n">
-        <v>7532</v>
+        <v>10864</v>
       </c>
       <c r="K24" s="16" t="n">
-        <v>6566</v>
+        <v>9399</v>
       </c>
       <c r="L24" s="16" t="n">
-        <v>17418</v>
+        <v>23583</v>
       </c>
       <c r="M24" s="16" t="n">
-        <v>5865</v>
+        <v>7647</v>
       </c>
       <c r="N24" s="16" t="n">
-        <v>7532</v>
+        <v>10864</v>
       </c>
       <c r="O24" s="16" t="n">
-        <v>13397</v>
+        <v>18511</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>4021</v>
+        <v>5072</v>
       </c>
       <c r="Q24" s="16" t="n">
-        <v>4021</v>
+        <v>5072</v>
       </c>
       <c r="R24" s="16" t="n">
         <v>0</v>
@@ -2532,28 +2532,28 @@
         <v>0</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>8485</v>
+        <v>9985</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>13483</v>
+        <v>16883</v>
       </c>
       <c r="L27" s="19" t="n">
-        <v>36238</v>
+        <v>41138</v>
       </c>
       <c r="M27" s="19" t="n">
         <v>12576</v>
       </c>
       <c r="N27" s="19" t="n">
-        <v>8485</v>
+        <v>9985</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>21061</v>
+        <v>22561</v>
       </c>
       <c r="P27" s="19" t="n">
-        <v>15177</v>
+        <v>18577</v>
       </c>
       <c r="Q27" s="19" t="n">
-        <v>15177</v>
+        <v>18577</v>
       </c>
       <c r="R27" s="19" t="n">
         <v>0</v>
@@ -2674,28 +2674,28 @@
         <v>0</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>9125</v>
+        <v>11075</v>
       </c>
       <c r="K29" s="19" t="n">
         <v>8360</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>46424</v>
+        <v>48374</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>9339</v>
+        <v>11139</v>
       </c>
       <c r="N29" s="19" t="n">
-        <v>9125</v>
+        <v>11075</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>18464</v>
+        <v>22214</v>
       </c>
       <c r="P29" s="19" t="n">
-        <v>27960</v>
+        <v>26160</v>
       </c>
       <c r="Q29" s="19" t="n">
-        <v>27960</v>
+        <v>26160</v>
       </c>
       <c r="R29" s="19" t="n">
         <v>0</v>
@@ -2887,28 +2887,28 @@
         <v>0</v>
       </c>
       <c r="J32" s="16" t="n">
-        <v>11022</v>
+        <v>13822</v>
       </c>
       <c r="K32" s="16" t="n">
         <v>20910</v>
       </c>
       <c r="L32" s="16" t="n">
-        <v>32302</v>
+        <v>35102</v>
       </c>
       <c r="M32" s="16" t="n">
-        <v>10716</v>
+        <v>12498</v>
       </c>
       <c r="N32" s="16" t="n">
-        <v>11022</v>
+        <v>13822</v>
       </c>
       <c r="O32" s="16" t="n">
-        <v>21738</v>
+        <v>26320</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>10564</v>
+        <v>8782</v>
       </c>
       <c r="Q32" s="16" t="n">
-        <v>10564</v>
+        <v>8782</v>
       </c>
       <c r="R32" s="16" t="n">
         <v>0</v>
@@ -3180,19 +3180,19 @@
         <v>10671</v>
       </c>
       <c r="M36" s="16" t="n">
-        <v>9721</v>
+        <v>10221</v>
       </c>
       <c r="N36" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O36" s="16" t="n">
-        <v>9721</v>
+        <v>10221</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>950</v>
+        <v>450</v>
       </c>
       <c r="Q36" s="16" t="n">
-        <v>950</v>
+        <v>450</v>
       </c>
       <c r="R36" s="16" t="n">
         <v>0</v>
@@ -3316,25 +3316,25 @@
         <v>0</v>
       </c>
       <c r="K38" s="16" t="n">
-        <v>5865</v>
+        <v>7647</v>
       </c>
       <c r="L38" s="16" t="n">
-        <v>5865</v>
+        <v>7647</v>
       </c>
       <c r="M38" s="16" t="n">
-        <v>1905</v>
+        <v>3749</v>
       </c>
       <c r="N38" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="16" t="n">
-        <v>1905</v>
+        <v>3749</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>3960</v>
+        <v>3898</v>
       </c>
       <c r="Q38" s="16" t="n">
-        <v>3960</v>
+        <v>3898</v>
       </c>
       <c r="R38" s="16" t="n">
         <v>0</v>
@@ -3455,28 +3455,28 @@
         <v>0</v>
       </c>
       <c r="J40" s="16" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K40" s="16" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="L40" s="16" t="n">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="M40" s="16" t="n">
         <v>5000</v>
       </c>
       <c r="N40" s="16" t="n">
+        <v>10000</v>
+      </c>
+      <c r="O40" s="16" t="n">
+        <v>15000</v>
+      </c>
+      <c r="P40" s="16" t="n">
         <v>5000</v>
       </c>
-      <c r="O40" s="16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P40" s="16" t="n">
-        <v>0</v>
-      </c>
       <c r="Q40" s="16" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="R40" s="16" t="n">
         <v>0</v>
@@ -3810,28 +3810,28 @@
         <v>0</v>
       </c>
       <c r="J45" s="19" t="n">
-        <v>18425</v>
+        <v>27425</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>7000</v>
+        <v>16000</v>
       </c>
       <c r="L45" s="19" t="n">
-        <v>47247</v>
+        <v>65247</v>
       </c>
       <c r="M45" s="19" t="n">
-        <v>5220</v>
+        <v>7420</v>
       </c>
       <c r="N45" s="19" t="n">
-        <v>18425</v>
+        <v>27425</v>
       </c>
       <c r="O45" s="19" t="n">
-        <v>24072</v>
+        <v>35272</v>
       </c>
       <c r="P45" s="19" t="n">
-        <v>23175</v>
+        <v>29975</v>
       </c>
       <c r="Q45" s="19" t="n">
-        <v>23175</v>
+        <v>29975</v>
       </c>
       <c r="R45" s="19" t="n">
         <v>0</v>
@@ -4094,22 +4094,22 @@
         <v>0</v>
       </c>
       <c r="J49" s="19" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="L49" s="19" t="n">
-        <v>14830</v>
+        <v>14928</v>
       </c>
       <c r="M49" s="19" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="N49" s="19" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="O49" s="19" t="n">
-        <v>14830</v>
+        <v>14928</v>
       </c>
       <c r="P49" s="19" t="n">
         <v>0</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="J50" s="16" t="n">
-        <v>10297</v>
+        <v>13397</v>
       </c>
       <c r="K50" s="16" t="n">
-        <v>10297</v>
+        <v>13397</v>
       </c>
       <c r="L50" s="16" t="n">
-        <v>20719</v>
+        <v>26919</v>
       </c>
       <c r="M50" s="16" t="n">
         <v>10099</v>
       </c>
       <c r="N50" s="16" t="n">
-        <v>10322</v>
+        <v>13422</v>
       </c>
       <c r="O50" s="16" t="n">
-        <v>20421</v>
+        <v>23521</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>298</v>
+        <v>3398</v>
       </c>
       <c r="Q50" s="16" t="n">
-        <v>298</v>
+        <v>3398</v>
       </c>
       <c r="R50" s="16" t="n">
         <v>0</v>
@@ -4310,25 +4310,25 @@
         <v>0</v>
       </c>
       <c r="K52" s="16" t="n">
-        <v>21012</v>
+        <v>21912</v>
       </c>
       <c r="L52" s="16" t="n">
-        <v>30016</v>
+        <v>30916</v>
       </c>
       <c r="M52" s="16" t="n">
-        <v>21539</v>
+        <v>21588</v>
       </c>
       <c r="N52" s="16" t="n">
         <v>85</v>
       </c>
       <c r="O52" s="16" t="n">
-        <v>21624</v>
+        <v>21673</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>8392</v>
+        <v>9243</v>
       </c>
       <c r="Q52" s="16" t="n">
-        <v>8392</v>
+        <v>9243</v>
       </c>
       <c r="R52" s="16" t="n">
         <v>0</v>
@@ -4523,10 +4523,10 @@
         <v>0</v>
       </c>
       <c r="K55" s="19" t="n">
-        <v>8034</v>
+        <v>9374</v>
       </c>
       <c r="L55" s="19" t="n">
-        <v>17117</v>
+        <v>18457</v>
       </c>
       <c r="M55" s="19" t="n">
         <v>14628</v>
@@ -4538,10 +4538,10 @@
         <v>14628</v>
       </c>
       <c r="P55" s="19" t="n">
-        <v>2489</v>
+        <v>3829</v>
       </c>
       <c r="Q55" s="19" t="n">
-        <v>2489</v>
+        <v>3829</v>
       </c>
       <c r="R55" s="19" t="n">
         <v>0</v>
@@ -4594,25 +4594,25 @@
         <v>0</v>
       </c>
       <c r="K56" s="16" t="n">
-        <v>10465</v>
+        <v>12035</v>
       </c>
       <c r="L56" s="16" t="n">
-        <v>20420</v>
+        <v>21990</v>
       </c>
       <c r="M56" s="16" t="n">
-        <v>12191</v>
+        <v>12240</v>
       </c>
       <c r="N56" s="16" t="n">
         <v>85</v>
       </c>
       <c r="O56" s="16" t="n">
-        <v>12276</v>
+        <v>12325</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>8144</v>
+        <v>9665</v>
       </c>
       <c r="Q56" s="16" t="n">
-        <v>8144</v>
+        <v>9665</v>
       </c>
       <c r="R56" s="16" t="n">
         <v>0</v>
@@ -4813,19 +4813,19 @@
         <v>17218</v>
       </c>
       <c r="M59" s="19" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="N59" s="19" t="n">
         <v>7181</v>
       </c>
       <c r="O59" s="19" t="n">
-        <v>14670</v>
+        <v>14719</v>
       </c>
       <c r="P59" s="19" t="n">
-        <v>2548</v>
+        <v>2499</v>
       </c>
       <c r="Q59" s="19" t="n">
-        <v>2548</v>
+        <v>2499</v>
       </c>
       <c r="R59" s="19" t="n">
         <v>0</v>
@@ -4875,28 +4875,28 @@
         <v>0</v>
       </c>
       <c r="J60" s="16" t="n">
-        <v>10070</v>
+        <v>13070</v>
       </c>
       <c r="K60" s="16" t="n">
-        <v>6920</v>
+        <v>9920</v>
       </c>
       <c r="L60" s="16" t="n">
-        <v>22173</v>
+        <v>28173</v>
       </c>
       <c r="M60" s="16" t="n">
         <v>10099</v>
       </c>
       <c r="N60" s="16" t="n">
-        <v>10095</v>
+        <v>13095</v>
       </c>
       <c r="O60" s="16" t="n">
-        <v>20484</v>
+        <v>23484</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>1689</v>
+        <v>4689</v>
       </c>
       <c r="Q60" s="16" t="n">
-        <v>1689</v>
+        <v>4689</v>
       </c>
       <c r="R60" s="16" t="n">
         <v>0</v>
@@ -5020,25 +5020,25 @@
         <v>0</v>
       </c>
       <c r="K62" s="16" t="n">
-        <v>14060</v>
+        <v>14420</v>
       </c>
       <c r="L62" s="16" t="n">
-        <v>15868</v>
+        <v>16228</v>
       </c>
       <c r="M62" s="16" t="n">
-        <v>12224</v>
+        <v>12273</v>
       </c>
       <c r="N62" s="16" t="n">
         <v>85</v>
       </c>
       <c r="O62" s="16" t="n">
-        <v>12309</v>
+        <v>12358</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>3559</v>
+        <v>3870</v>
       </c>
       <c r="Q62" s="16" t="n">
-        <v>3559</v>
+        <v>3870</v>
       </c>
       <c r="R62" s="16" t="n">
         <v>0</v>
@@ -5230,28 +5230,28 @@
         <v>0</v>
       </c>
       <c r="J65" s="19" t="n">
-        <v>10880</v>
+        <v>14330</v>
       </c>
       <c r="K65" s="19" t="n">
-        <v>11930</v>
+        <v>14930</v>
       </c>
       <c r="L65" s="19" t="n">
-        <v>22810</v>
+        <v>29260</v>
       </c>
       <c r="M65" s="19" t="n">
-        <v>8930</v>
+        <v>12374</v>
       </c>
       <c r="N65" s="19" t="n">
-        <v>10880</v>
+        <v>14330</v>
       </c>
       <c r="O65" s="19" t="n">
-        <v>19810</v>
+        <v>26704</v>
       </c>
       <c r="P65" s="19" t="n">
-        <v>3000</v>
+        <v>2556</v>
       </c>
       <c r="Q65" s="19" t="n">
-        <v>3000</v>
+        <v>2556</v>
       </c>
       <c r="R65" s="19" t="n">
         <v>0</v>
@@ -5381,19 +5381,19 @@
         <v>65612</v>
       </c>
       <c r="M67" s="19" t="n">
-        <v>14456</v>
+        <v>14816</v>
       </c>
       <c r="N67" s="19" t="n">
         <v>17833</v>
       </c>
       <c r="O67" s="19" t="n">
-        <v>32289</v>
+        <v>32649</v>
       </c>
       <c r="P67" s="19" t="n">
-        <v>33323</v>
+        <v>32963</v>
       </c>
       <c r="Q67" s="19" t="n">
-        <v>33323</v>
+        <v>32963</v>
       </c>
       <c r="R67" s="19" t="n">
         <v>0</v>
@@ -5446,25 +5446,25 @@
         <v>0</v>
       </c>
       <c r="K68" s="16" t="n">
-        <v>47012</v>
+        <v>79212</v>
       </c>
       <c r="L68" s="16" t="n">
-        <v>48362</v>
+        <v>80562</v>
       </c>
       <c r="M68" s="16" t="n">
-        <v>48158.8</v>
+        <v>79590.8</v>
       </c>
       <c r="N68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O68" s="16" t="n">
-        <v>48158.8</v>
+        <v>79590.8</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>203.2</v>
+        <v>971.2</v>
       </c>
       <c r="Q68" s="16" t="n">
-        <v>203.2</v>
+        <v>971.2</v>
       </c>
       <c r="R68" s="16" t="n">
         <v>-0</v>
@@ -5594,19 +5594,19 @@
         <v>46008</v>
       </c>
       <c r="M70" s="16" t="n">
-        <v>19374</v>
+        <v>19423</v>
       </c>
       <c r="N70" s="16" t="n">
         <v>85</v>
       </c>
       <c r="O70" s="16" t="n">
-        <v>19459</v>
+        <v>19508</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>26549</v>
+        <v>26500</v>
       </c>
       <c r="Q70" s="16" t="n">
-        <v>26549</v>
+        <v>26500</v>
       </c>
       <c r="R70" s="16" t="n">
         <v>0</v>
@@ -5798,28 +5798,28 @@
         <v>0</v>
       </c>
       <c r="J73" s="19" t="n">
-        <v>10465</v>
+        <v>12035</v>
       </c>
       <c r="K73" s="19" t="n">
         <v>10195</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>39551</v>
+        <v>41121</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>10465</v>
+        <v>12035</v>
       </c>
       <c r="N73" s="19" t="n">
-        <v>10465</v>
+        <v>12035</v>
       </c>
       <c r="O73" s="19" t="n">
-        <v>20930</v>
+        <v>24070</v>
       </c>
       <c r="P73" s="19" t="n">
-        <v>18621</v>
+        <v>17051</v>
       </c>
       <c r="Q73" s="19" t="n">
-        <v>18621</v>
+        <v>17051</v>
       </c>
       <c r="R73" s="19" t="n">
         <v>0</v>
@@ -5869,28 +5869,28 @@
         <v>0</v>
       </c>
       <c r="J74" s="16" t="n">
-        <v>8034</v>
+        <v>9374</v>
       </c>
       <c r="K74" s="16" t="n">
-        <v>8930</v>
+        <v>12374</v>
       </c>
       <c r="L74" s="16" t="n">
-        <v>16964</v>
+        <v>21748</v>
       </c>
       <c r="M74" s="16" t="n">
-        <v>8034</v>
+        <v>9374</v>
       </c>
       <c r="N74" s="16" t="n">
-        <v>8034</v>
+        <v>9374</v>
       </c>
       <c r="O74" s="16" t="n">
-        <v>16068</v>
+        <v>18748</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>896</v>
+        <v>3000</v>
       </c>
       <c r="Q74" s="16" t="n">
-        <v>896</v>
+        <v>3000</v>
       </c>
       <c r="R74" s="16" t="n">
         <v>0</v>
@@ -6014,10 +6014,10 @@
         <v>7695</v>
       </c>
       <c r="K76" s="16" t="n">
-        <v>9721</v>
+        <v>10221</v>
       </c>
       <c r="L76" s="16" t="n">
-        <v>19872</v>
+        <v>20372</v>
       </c>
       <c r="M76" s="16" t="n">
         <v>8107</v>
@@ -6029,10 +6029,10 @@
         <v>15810</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>4062</v>
+        <v>4562</v>
       </c>
       <c r="Q76" s="16" t="n">
-        <v>4062</v>
+        <v>4562</v>
       </c>
       <c r="R76" s="16" t="n">
         <v>0</v>
@@ -6082,28 +6082,28 @@
         <v>0</v>
       </c>
       <c r="J77" s="19" t="n">
-        <v>3665</v>
+        <v>4808</v>
       </c>
       <c r="K77" s="19" t="n">
         <v>4755</v>
       </c>
       <c r="L77" s="19" t="n">
-        <v>8494</v>
+        <v>9637</v>
       </c>
       <c r="M77" s="19" t="n">
-        <v>2070</v>
+        <v>3730</v>
       </c>
       <c r="N77" s="19" t="n">
-        <v>3665</v>
+        <v>4808</v>
       </c>
       <c r="O77" s="19" t="n">
-        <v>5735</v>
+        <v>8538</v>
       </c>
       <c r="P77" s="19" t="n">
-        <v>2759</v>
+        <v>1099</v>
       </c>
       <c r="Q77" s="19" t="n">
-        <v>2759</v>
+        <v>1099</v>
       </c>
       <c r="R77" s="19" t="n">
         <v>0</v>
@@ -6153,28 +6153,28 @@
         <v>0</v>
       </c>
       <c r="J78" s="16" t="n">
-        <v>3554</v>
+        <v>5409</v>
       </c>
       <c r="K78" s="16" t="n">
-        <v>1905</v>
+        <v>3749</v>
       </c>
       <c r="L78" s="16" t="n">
-        <v>7730</v>
+        <v>11429</v>
       </c>
       <c r="M78" s="16" t="n">
-        <v>4150</v>
+        <v>5520</v>
       </c>
       <c r="N78" s="16" t="n">
-        <v>3554</v>
+        <v>5409</v>
       </c>
       <c r="O78" s="16" t="n">
-        <v>7706</v>
+        <v>10931</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>24</v>
+        <v>498</v>
       </c>
       <c r="Q78" s="16" t="n">
-        <v>24</v>
+        <v>498</v>
       </c>
       <c r="R78" s="16" t="n">
         <v>0</v>
@@ -6304,19 +6304,19 @@
         <v>9846</v>
       </c>
       <c r="M80" s="16" t="n">
-        <v>4414</v>
+        <v>4923</v>
       </c>
       <c r="N80" s="16" t="n">
         <v>4923</v>
       </c>
       <c r="O80" s="16" t="n">
-        <v>9337</v>
+        <v>9846</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="Q80" s="16" t="n">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="R80" s="16" t="n">
         <v>0</v>
@@ -6508,22 +6508,22 @@
         <v>0</v>
       </c>
       <c r="J83" s="19" t="n">
-        <v>354</v>
+        <v>404</v>
       </c>
       <c r="K83" s="19" t="n">
         <v>100</v>
       </c>
       <c r="L83" s="19" t="n">
-        <v>803</v>
+        <v>885</v>
       </c>
       <c r="M83" s="19" t="n">
         <v>0</v>
       </c>
       <c r="N83" s="19" t="n">
-        <v>356</v>
+        <v>406</v>
       </c>
       <c r="O83" s="19" t="n">
-        <v>356</v>
+        <v>438</v>
       </c>
       <c r="P83" s="19" t="n">
         <v>447</v>
@@ -6656,7 +6656,7 @@
         <v>4600</v>
       </c>
       <c r="L85" s="19" t="n">
-        <v>19214</v>
+        <v>19250</v>
       </c>
       <c r="M85" s="19" t="n">
         <v>7150</v>
@@ -6665,7 +6665,7 @@
         <v>5700</v>
       </c>
       <c r="O85" s="19" t="n">
-        <v>12851</v>
+        <v>12887</v>
       </c>
       <c r="P85" s="19" t="n">
         <v>6363</v>
@@ -6721,28 +6721,28 @@
         <v>0</v>
       </c>
       <c r="J86" s="16" t="n">
-        <v>1781</v>
+        <v>1830</v>
       </c>
       <c r="K86" s="16" t="n">
         <v>4200</v>
       </c>
       <c r="L86" s="16" t="n">
-        <v>7291</v>
+        <v>7357</v>
       </c>
       <c r="M86" s="16" t="n">
-        <v>2125</v>
+        <v>2174</v>
       </c>
       <c r="N86" s="16" t="n">
-        <v>1841</v>
+        <v>1890</v>
       </c>
       <c r="O86" s="16" t="n">
-        <v>4078</v>
+        <v>4193</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>3213</v>
+        <v>3164</v>
       </c>
       <c r="Q86" s="16" t="n">
-        <v>3213</v>
+        <v>3164</v>
       </c>
       <c r="R86" s="16" t="n">
         <v>0</v>
@@ -6792,28 +6792,28 @@
         <v>0</v>
       </c>
       <c r="J87" s="19" t="n">
-        <v>10996</v>
+        <v>12596</v>
       </c>
       <c r="K87" s="19" t="n">
-        <v>5140</v>
+        <v>7340</v>
       </c>
       <c r="L87" s="19" t="n">
-        <v>27246</v>
+        <v>31123</v>
       </c>
       <c r="M87" s="19" t="n">
         <v>9415</v>
       </c>
       <c r="N87" s="19" t="n">
-        <v>10996</v>
+        <v>12596</v>
       </c>
       <c r="O87" s="19" t="n">
-        <v>20486</v>
+        <v>22163</v>
       </c>
       <c r="P87" s="19" t="n">
-        <v>6760</v>
+        <v>8960</v>
       </c>
       <c r="Q87" s="19" t="n">
-        <v>6760</v>
+        <v>8960</v>
       </c>
       <c r="R87" s="19" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>6065</v>
       </c>
       <c r="L89" s="19" t="n">
-        <v>15463</v>
+        <v>15516</v>
       </c>
       <c r="M89" s="19" t="n">
         <v>5290</v>
@@ -6949,7 +6949,7 @@
         <v>5307</v>
       </c>
       <c r="O89" s="19" t="n">
-        <v>10626</v>
+        <v>10679</v>
       </c>
       <c r="P89" s="19" t="n">
         <v>4837</v>
@@ -7147,22 +7147,22 @@
         <v>0</v>
       </c>
       <c r="J92" s="16" t="n">
-        <v>305</v>
+        <v>355</v>
       </c>
       <c r="K92" s="16" t="n">
         <v>100</v>
       </c>
       <c r="L92" s="16" t="n">
-        <v>912</v>
+        <v>993</v>
       </c>
       <c r="M92" s="16" t="n">
         <v>0</v>
       </c>
       <c r="N92" s="16" t="n">
-        <v>307</v>
+        <v>357</v>
       </c>
       <c r="O92" s="16" t="n">
-        <v>313</v>
+        <v>394</v>
       </c>
       <c r="P92" s="16" t="n">
         <v>599</v>
@@ -7295,7 +7295,7 @@
         <v>4800</v>
       </c>
       <c r="L94" s="16" t="n">
-        <v>19826</v>
+        <v>19961</v>
       </c>
       <c r="M94" s="16" t="n">
         <v>7150</v>
@@ -7304,7 +7304,7 @@
         <v>5582</v>
       </c>
       <c r="O94" s="16" t="n">
-        <v>12732</v>
+        <v>12867</v>
       </c>
       <c r="P94" s="16" t="n">
         <v>7094</v>
@@ -7360,28 +7360,28 @@
         <v>0</v>
       </c>
       <c r="J95" s="19" t="n">
-        <v>1763</v>
+        <v>1812</v>
       </c>
       <c r="K95" s="19" t="n">
         <v>3430</v>
       </c>
       <c r="L95" s="19" t="n">
-        <v>6767</v>
+        <v>6828</v>
       </c>
       <c r="M95" s="19" t="n">
-        <v>2125</v>
+        <v>2174</v>
       </c>
       <c r="N95" s="19" t="n">
-        <v>1823</v>
+        <v>1872</v>
       </c>
       <c r="O95" s="19" t="n">
-        <v>4043</v>
+        <v>4153</v>
       </c>
       <c r="P95" s="19" t="n">
-        <v>2724</v>
+        <v>2675</v>
       </c>
       <c r="Q95" s="19" t="n">
-        <v>2724</v>
+        <v>2675</v>
       </c>
       <c r="R95" s="19" t="n">
         <v>0</v>
@@ -7431,28 +7431,28 @@
         <v>0</v>
       </c>
       <c r="J96" s="16" t="n">
-        <v>11199</v>
+        <v>12199</v>
       </c>
       <c r="K96" s="16" t="n">
-        <v>6005</v>
+        <v>8005</v>
       </c>
       <c r="L96" s="16" t="n">
-        <v>24220</v>
+        <v>27269</v>
       </c>
       <c r="M96" s="16" t="n">
         <v>9415</v>
       </c>
       <c r="N96" s="16" t="n">
-        <v>11199</v>
+        <v>12199</v>
       </c>
       <c r="O96" s="16" t="n">
-        <v>20667</v>
+        <v>21716</v>
       </c>
       <c r="P96" s="16" t="n">
-        <v>3553</v>
+        <v>5553</v>
       </c>
       <c r="Q96" s="16" t="n">
-        <v>3553</v>
+        <v>5553</v>
       </c>
       <c r="R96" s="16" t="n">
         <v>0</v>
@@ -7579,7 +7579,7 @@
         <v>5856</v>
       </c>
       <c r="L98" s="16" t="n">
-        <v>15356</v>
+        <v>15373</v>
       </c>
       <c r="M98" s="16" t="n">
         <v>5290</v>
@@ -7588,7 +7588,7 @@
         <v>5587</v>
       </c>
       <c r="O98" s="16" t="n">
-        <v>10903</v>
+        <v>10920</v>
       </c>
       <c r="P98" s="16" t="n">
         <v>4453</v>
@@ -7715,28 +7715,28 @@
         <v>0</v>
       </c>
       <c r="J100" s="16" t="n">
-        <v>0</v>
+        <v>15040</v>
       </c>
       <c r="K100" s="16" t="n">
-        <v>13306</v>
+        <v>16810</v>
       </c>
       <c r="L100" s="16" t="n">
-        <v>13306</v>
+        <v>31850</v>
       </c>
       <c r="M100" s="16" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="N100" s="16" t="n">
-        <v>0</v>
+        <v>15040</v>
       </c>
       <c r="O100" s="16" t="n">
-        <v>0</v>
+        <v>15980</v>
       </c>
       <c r="P100" s="16" t="n">
-        <v>13306</v>
+        <v>15870</v>
       </c>
       <c r="Q100" s="16" t="n">
-        <v>13306</v>
+        <v>15870</v>
       </c>
       <c r="R100" s="16" t="n">
         <v>0</v>
@@ -7786,22 +7786,22 @@
         <v>0</v>
       </c>
       <c r="J101" s="19" t="n">
-        <v>4380</v>
+        <v>8663</v>
       </c>
       <c r="K101" s="19" t="n">
         <v>8663</v>
       </c>
       <c r="L101" s="19" t="n">
-        <v>24243</v>
+        <v>28526</v>
       </c>
       <c r="M101" s="19" t="n">
         <v>14750</v>
       </c>
       <c r="N101" s="19" t="n">
-        <v>4380</v>
+        <v>8663</v>
       </c>
       <c r="O101" s="19" t="n">
-        <v>19130</v>
+        <v>23413</v>
       </c>
       <c r="P101" s="19" t="n">
         <v>5113</v>
@@ -7857,28 +7857,28 @@
         <v>0</v>
       </c>
       <c r="J102" s="16" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="K102" s="16" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="L102" s="16" t="n">
-        <v>13606</v>
+        <v>15486</v>
       </c>
       <c r="M102" s="16" t="n">
         <v>4840</v>
       </c>
       <c r="N102" s="16" t="n">
-        <v>0</v>
+        <v>940</v>
       </c>
       <c r="O102" s="16" t="n">
-        <v>4840</v>
+        <v>5780</v>
       </c>
       <c r="P102" s="16" t="n">
-        <v>8766</v>
+        <v>9706</v>
       </c>
       <c r="Q102" s="16" t="n">
-        <v>8766</v>
+        <v>9706</v>
       </c>
       <c r="R102" s="16" t="n">
         <v>0</v>
@@ -8008,19 +8008,19 @@
         <v>71160</v>
       </c>
       <c r="M104" s="16" t="n">
-        <v>6920</v>
+        <v>9920</v>
       </c>
       <c r="N104" s="16" t="n">
         <v>14750</v>
       </c>
       <c r="O104" s="16" t="n">
-        <v>21670</v>
+        <v>24670</v>
       </c>
       <c r="P104" s="16" t="n">
-        <v>49490</v>
+        <v>46490</v>
       </c>
       <c r="Q104" s="16" t="n">
-        <v>49490</v>
+        <v>46490</v>
       </c>
       <c r="R104" s="16" t="n">
         <v>0</v>
@@ -8141,28 +8141,28 @@
         <v>0</v>
       </c>
       <c r="J106" s="16" t="n">
-        <v>12000</v>
+        <v>17000</v>
       </c>
       <c r="K106" s="16" t="n">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="L106" s="16" t="n">
-        <v>18000</v>
+        <v>28000</v>
       </c>
       <c r="M106" s="16" t="n">
         <v>4800</v>
       </c>
       <c r="N106" s="16" t="n">
-        <v>12000</v>
+        <v>17000</v>
       </c>
       <c r="O106" s="16" t="n">
-        <v>16800</v>
+        <v>21800</v>
       </c>
       <c r="P106" s="16" t="n">
-        <v>1200</v>
+        <v>6200</v>
       </c>
       <c r="Q106" s="16" t="n">
-        <v>1200</v>
+        <v>6200</v>
       </c>
       <c r="R106" s="16" t="n">
         <v>0</v>
@@ -8425,28 +8425,28 @@
         <v>0</v>
       </c>
       <c r="J110" s="16" t="n">
-        <v>24692</v>
+        <v>34692</v>
       </c>
       <c r="K110" s="16" t="n">
-        <v>7000</v>
+        <v>17000</v>
       </c>
       <c r="L110" s="16" t="n">
-        <v>59443</v>
+        <v>79443</v>
       </c>
       <c r="M110" s="16" t="n">
-        <v>6085</v>
+        <v>8085</v>
       </c>
       <c r="N110" s="16" t="n">
-        <v>24692</v>
+        <v>34692</v>
       </c>
       <c r="O110" s="16" t="n">
-        <v>31142</v>
+        <v>43142</v>
       </c>
       <c r="P110" s="16" t="n">
-        <v>28301</v>
+        <v>36301</v>
       </c>
       <c r="Q110" s="16" t="n">
-        <v>28301</v>
+        <v>36301</v>
       </c>
       <c r="R110" s="16" t="n">
         <v>0</v>
@@ -8647,19 +8647,19 @@
         <v>10589</v>
       </c>
       <c r="M113" s="19" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="N113" s="19" t="n">
         <v>0</v>
       </c>
       <c r="O113" s="19" t="n">
-        <v>7415</v>
+        <v>7464</v>
       </c>
       <c r="P113" s="19" t="n">
-        <v>3174</v>
+        <v>3125</v>
       </c>
       <c r="Q113" s="19" t="n">
-        <v>3174</v>
+        <v>3125</v>
       </c>
       <c r="R113" s="19" t="n">
         <v>0</v>
@@ -8712,25 +8712,25 @@
         <v>0</v>
       </c>
       <c r="K114" s="16" t="n">
-        <v>9339</v>
+        <v>11139</v>
       </c>
       <c r="L114" s="16" t="n">
-        <v>20913</v>
+        <v>22713</v>
       </c>
       <c r="M114" s="16" t="n">
-        <v>10297</v>
+        <v>13397</v>
       </c>
       <c r="N114" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O114" s="16" t="n">
-        <v>10297</v>
+        <v>13397</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>10616</v>
+        <v>9316</v>
       </c>
       <c r="Q114" s="16" t="n">
-        <v>10616</v>
+        <v>9316</v>
       </c>
       <c r="R114" s="16" t="n">
         <v>0</v>
@@ -8831,15 +8831,15 @@
       <c r="J116" s="20" t="n"/>
       <c r="K116" s="20" t="n"/>
       <c r="L116" s="21" t="n">
-        <v>1428162.821</v>
+        <v>1626125.821</v>
       </c>
       <c r="M116" s="20" t="n"/>
       <c r="N116" s="20" t="n"/>
       <c r="O116" s="21" t="n">
-        <v>988868.3</v>
+        <v>1147598.3</v>
       </c>
       <c r="P116" s="21" t="n">
-        <v>439294.521</v>
+        <v>478527.521</v>
       </c>
       <c r="Q116" s="20" t="n"/>
       <c r="R116" s="20" t="n"/>
